--- a/output/pdf_financials_xlsx/GMV.xlsx
+++ b/output/pdf_financials_xlsx/GMV.xlsx
@@ -4508,34 +4508,34 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.740523</v>
+        <v>1.667903</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>4.314798</v>
+        <v>8.727855</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>4.402621</v>
+        <v>8.877155</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>4.890008</v>
+        <v>9.997140999999999</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>5.362089</v>
+        <v>10.886326</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>6.905177</v>
+        <v>13.88287</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>6.94596</v>
+        <v>13.994543</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>8.171491</v>
+        <v>16.537244</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>8.518686000000001</v>
+        <v>17.179427</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>7.849802</v>
+        <v>15.796186</v>
       </c>
     </row>
     <row r="92">

--- a/output/pdf_financials_xlsx/GMV.xlsx
+++ b/output/pdf_financials_xlsx/GMV.xlsx
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0133</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002991</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.608498</v>
+        <v>-0.621798</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.965053</v>
+        <v>-0.968044</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.412747</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.608498</v>
+        <v>-0.621798</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.965053</v>
+        <v>-0.968044</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.412747</v>
@@ -6876,7 +6876,11 @@
           <t>Reclamation Deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -8042,7 +8046,11 @@
           <t>Reclamation Deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -8634,7 +8642,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -9478,7 +9486,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.006028</v>
       </c>
@@ -11822,7 +11834,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -12392,7 +12408,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -12836,7 +12856,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -22222,7 +22246,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">

--- a/output/pdf_financials_xlsx/GMV.xlsx
+++ b/output/pdf_financials_xlsx/GMV.xlsx
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.041202</v>
+        <v>0.291665</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.052709</v>
+        <v>0.281959</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.294058</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.065744</v>
+        <v>0.316207</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.4119</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.001547</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.01029</v>
@@ -5573,13 +5573,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.130878</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.03915</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.005103</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -10806,7 +10806,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13762,7 +13766,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -14286,7 +14294,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -14360,7 +14372,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -16050,7 +16066,11 @@
           <t>Net proceeds from private placement</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -20568,7 +20588,11 @@
           <t>Management and directors fees $</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -21248,7 +21272,11 @@
           <t>Management and directors fees (Note 10) $</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E204" s="5" t="n">
         <v>0.235875</v>
       </c>
@@ -21784,7 +21812,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E211" s="5" t="n">
         <v>0.014588</v>
       </c>
